--- a/src/tcs_smart_analyzer/config/interface_mapping.xlsx
+++ b/src/tcs_smart_analyzer/config/interface_mapping.xlsx
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -766,6 +766,22 @@
           <t>actual_signal_name_5</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>yawrate</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>YawRate</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -858,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1025,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>yawrate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/tcs_smart_analyzer/config/interface_mapping.xlsx
+++ b/src/tcs_smart_analyzer/config/interface_mapping.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自定义信号" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考信息" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_metadata" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,16 +420,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,278 +439,500 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>actual_signal_name_1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>actual_signal_name_2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>actual_signal_name_3</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_4</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>longitudinal_accel_mps2</t>
+          <t>time_s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KPI: max_jerk_mps3
-KPI: vehicle_shake_intensity</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Lgt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr"/>
+          <t>时间轴，单位 s，必须配置且固定排在第一行。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>派生量: abs_target_slip_kph
+派生量: tcs_target_slip_kph
+KPI: abs_ctrl_time_max_s
+KPI: max_jerk_mps3
+KPI: tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tcs_active_fl</t>
+          <t>abs_active_fl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>派生量: tcs_target_slip_ratio_global
-KPI: tcs_max_control_time</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>TcsActiv(1)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr"/>
+          <t>左前轮 ABS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>派生量: abs_target_slip_kph
+KPI: abs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>AbsActiv(1)</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
-      <c r="G3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tcs_active_fr</t>
+          <t>abs_active_fr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>派生量: tcs_target_slip_ratio_global
-KPI: tcs_max_control_time</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>TcsActiv(2)</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr"/>
+          <t>右前轮 ABS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>派生量: abs_target_slip_kph
+KPI: abs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>AbsActiv(2)</t>
+        </is>
+      </c>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
-      <c r="G4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tcs_active_rl</t>
+          <t>abs_active_rl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>派生量: tcs_target_slip_ratio_global
-KPI: tcs_max_control_time</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>TcsActiv(3)</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr"/>
+          <t>左后轮 ABS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>派生量: abs_target_slip_kph
+KPI: abs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>AbsActiv(3)</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr"/>
-      <c r="G5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tcs_active_rr</t>
+          <t>abs_active_rr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>派生量: tcs_target_slip_ratio_global
-KPI: tcs_max_control_time</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>TcsActiv(4)</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr"/>
+          <t>右后轮 ABS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>派生量: abs_target_slip_kph
+KPI: abs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>AbsActiv(4)</t>
+        </is>
+      </c>
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr"/>
-      <c r="G6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time_s</t>
+          <t>accel_pedal_pct</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>派生量: tcs_target_slip_ratio_global
-KPI: max_jerk_mps3
-KPI: tcs_max_control_time</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr"/>
+          <t>油门开度，单位 %。</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KPI: mean_full_throttle_accel_mps2</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>YawRate+100</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vehicle_speed</t>
+          <t>brake_depth_pct</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>派生量: slip_ratio
-KPI: max_slip_speed
-KPI: mean_vehicle_speed_kph</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>SpdVeh</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr"/>
+          <t>制动深度，单位 %。</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KPI: mean_full_brake_decel_mps2</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>YawRate+100</t>
+        </is>
+      </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr"/>
-      <c r="G8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wheel_speed_fl</t>
+          <t>longitudinal_accel_mps2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>派生量: slip_ratio
-KPI: max_slip_speed</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>SpdWhl(1)</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr"/>
+          <t>纵向加速度，单位 m/s^2。</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KPI: max_jerk_mps3
+KPI: mean_full_brake_decel_mps2
+KPI: mean_full_throttle_accel_mps2
+KPI: shake_rms_mps2</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Lgt</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wheel_speed_fr</t>
+          <t>steering_wheel_angle_deg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>派生量: slip_ratio
-KPI: max_slip_speed</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>SpdWhl(2)</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr"/>
+          <t>方向盘转角，单位 deg。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KPI: max_steer_angle_deg</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>YawRate*0</t>
+        </is>
+      </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
-      <c r="G10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wheel_speed_rl</t>
+          <t>tcs_active_fl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>派生量: slip_ratio
-KPI: max_slip_speed</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>SpdWhl(3)</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr"/>
+          <t>左前轮 TCS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>派生量: tcs_target_slip_kph
+KPI: tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>TcsActiv(1)</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wheel_speed_rr</t>
+          <t>tcs_active_fr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>派生量: slip_ratio
-KPI: max_slip_speed</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>SpdWhl(4)</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr"/>
+          <t>右前轮 TCS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>派生量: tcs_target_slip_kph
+KPI: tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>TcsActiv(2)</t>
+        </is>
+      </c>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tcs_active_rl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>左后轮 TCS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>派生量: tcs_target_slip_kph
+KPI: tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>TcsActiv(3)</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tcs_active_rr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>右后轮 TCS 激活标志，布尔/0-1。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>派生量: tcs_target_slip_kph
+KPI: tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>TcsActiv(4)</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>车速，单位 kph。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>派生量: slip_kph</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>SpdVeh</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>wheel_speed_fl_kph</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>左前轮轮速，单位 kph。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>派生量: slip_kph</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>SpdWhl(1)</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>wheel_speed_fr_kph</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>右前轮轮速，单位 kph。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>派生量: slip_kph</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>SpdWhl(2)</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wheel_speed_rl_kph</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>左后轮轮速，单位 kph。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>派生量: slip_kph</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>SpdWhl(3)</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wheel_speed_rr_kph</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>右后轮轮速，单位 kph。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>派生量: slip_kph</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>SpdWhl(4)</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yaw_rate_degps</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>横摆角速度，单位 deg/s。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KPI: max_yaw_rate_degps</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>YawRate</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
@@ -724,15 +946,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -756,32 +976,6 @@
           <t>actual_signal_name_3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>yawrate</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>YawRate</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -822,7 +1016,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>系统信号 的 A-B 列只读，C-G 列可编辑；自定义信号 的 A-F 列均可编辑。</t>
+          <t>系统信号 的 A-C 列只读，后续真实信号名列可编辑；自定义信号 的第一列和真实信号名列均可编辑。</t>
         </is>
       </c>
     </row>
@@ -834,7 +1028,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>分析时只按 actual_signal_name_1 到 actual_signal_name_5 逐列匹配。系统信号的 From 列用于说明该 raw_inputs 名称被哪些 KPI / 派生量引用。</t>
+          <t>分析时会按 actual_signal_name_1 到当前最后一列依次匹配；单元格里既可以填实际信号名，也可以填公式表达式，例如 time_ms*0.001。系统信号的 Description 列自动展示物理意义与单位，From 列用于说明该 raw_inputs 名称被哪些 KPI / 派生量引用。</t>
         </is>
       </c>
     </row>
@@ -874,10 +1068,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -896,144 +1090,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>longitudinal_accel_mps2</t>
+          <t>time_s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KPI:max_jerk_mps3 | KPI:vehicle_shake_intensity</t>
+          <t>DERIVED:abs_target_slip_kph | DERIVED:tcs_target_slip_kph | KPI:abs_ctrl_time_max_s | KPI:max_jerk_mps3 | KPI:tcs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tcs_active_fl</t>
+          <t>abs_active_fl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DERIVED:tcs_target_slip_ratio_global | KPI:tcs_max_control_time</t>
+          <t>DERIVED:abs_target_slip_kph | KPI:abs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tcs_active_fr</t>
+          <t>abs_active_fr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DERIVED:tcs_target_slip_ratio_global | KPI:tcs_max_control_time</t>
+          <t>DERIVED:abs_target_slip_kph | KPI:abs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tcs_active_rl</t>
+          <t>abs_active_rl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DERIVED:tcs_target_slip_ratio_global | KPI:tcs_max_control_time</t>
+          <t>DERIVED:abs_target_slip_kph | KPI:abs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tcs_active_rr</t>
+          <t>abs_active_rr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DERIVED:tcs_target_slip_ratio_global | KPI:tcs_max_control_time</t>
+          <t>DERIVED:abs_target_slip_kph | KPI:abs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time_s</t>
+          <t>accel_pedal_pct</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DERIVED:tcs_target_slip_ratio_global | KPI:max_jerk_mps3 | KPI:tcs_max_control_time</t>
+          <t>KPI:mean_full_throttle_accel_mps2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vehicle_speed</t>
+          <t>brake_depth_pct</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DERIVED:slip_ratio | KPI:max_slip_speed | KPI:mean_vehicle_speed_kph</t>
+          <t>KPI:mean_full_brake_decel_mps2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wheel_speed_fl</t>
+          <t>longitudinal_accel_mps2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DERIVED:slip_ratio | KPI:max_slip_speed</t>
+          <t>KPI:max_jerk_mps3 | KPI:mean_full_brake_decel_mps2 | KPI:mean_full_throttle_accel_mps2 | KPI:shake_rms_mps2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wheel_speed_fr</t>
+          <t>steering_wheel_angle_deg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DERIVED:slip_ratio | KPI:max_slip_speed</t>
+          <t>KPI:max_steer_angle_deg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wheel_speed_rl</t>
+          <t>tcs_active_fl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DERIVED:slip_ratio | KPI:max_slip_speed</t>
+          <t>DERIVED:tcs_target_slip_kph | KPI:tcs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wheel_speed_rr</t>
+          <t>tcs_active_fr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DERIVED:slip_ratio | KPI:max_slip_speed</t>
+          <t>DERIVED:tcs_target_slip_kph | KPI:tcs_ctrl_time_max_s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>yawrate</t>
+          <t>tcs_active_rl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_defined</t>
+          <t>DERIVED:tcs_target_slip_kph | KPI:tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tcs_active_rr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DERIVED:tcs_target_slip_kph | KPI:tcs_ctrl_time_max_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vehicle_speed_kph</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DERIVED:slip_kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>wheel_speed_fl_kph</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DERIVED:slip_kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>wheel_speed_fr_kph</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DERIVED:slip_kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wheel_speed_rl_kph</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DERIVED:slip_kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wheel_speed_rr_kph</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DERIVED:slip_kph</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yaw_rate_degps</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KPI:max_yaw_rate_degps</t>
         </is>
       </c>
     </row>
@@ -1041,4 +1319,28 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>actual_signal_name_column_count</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/src/tcs_smart_analyzer/config/interface_mapping.xlsx
+++ b/src/tcs_smart_analyzer/config/interface_mapping.xlsx
@@ -424,7 +424,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>时间轴，单位 s，必须配置且固定排在第一行。</t>
+          <t>时间轴，单位 s。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/src/tcs_smart_analyzer/config/interface_mapping.xlsx
+++ b/src/tcs_smart_analyzer/config/interface_mapping.xlsx
@@ -424,7 +424,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>时间轴，单位 s，必须配置且固定排在第一行。</t>
+          <t>时间轴，单位 s。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -946,13 +946,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,6 +976,16 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>actual_signal_name_3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>actual_signal_name_4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actual_signal_name_5</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1349,27 @@
         </is>
       </c>
       <c r="B1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>system_actual_signal_name_column_count</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>custom_actual_signal_name_column_count</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/tcs_smart_analyzer/config/interface_mapping.xlsx
+++ b/src/tcs_smart_analyzer/config/interface_mapping.xlsx
@@ -946,15 +946,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,16 +974,6 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>actual_signal_name_3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_signal_name_5</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1337,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
@@ -1369,7 +1357,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
